--- a/transactions/Projection_de_projet_CLIENT.xlsx
+++ b/transactions/Projection_de_projet_CLIENT.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -111,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,8 +130,9 @@
     <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,13 +140,13 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -147,18 +154,31 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <i val="1"/>
+        <color rgb="00A6A6A6"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00F2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -257,6 +277,11 @@
         <t>Choisir FREEHOLD ou LEASEHOLD dans la liste deroulante.
 FREEHOLD -&gt; prix du terrain = surface x B19 (prix à l'are, sans durée).
 LEASEHOLD -&gt; prix du terrain = surface x B20 x B21 (prix à l'are et par an x durée).</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>Utilisee uniquement en LEASEHOLD. En FREEHOLD la cellule est grisee et n'entre dans aucun calcul.</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0" shapeId="0">
@@ -788,6 +813,10 @@
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
+      <c r="C19" s="12">
+        <f>IF($B$16="FREEHOLD",IF($B$19&gt;0,"","A RENSEIGNER"),"sans objet en LEASEHOLD")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -798,6 +827,10 @@
       <c r="B20" s="8" t="n">
         <v>5000000</v>
       </c>
+      <c r="C20" s="12">
+        <f>IF($B$16="LEASEHOLD",IF($B$20&gt;0,"","A RENSEIGNER"),"sans objet en FREEHOLD")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -808,6 +841,10 @@
       <c r="B21" s="10" t="n">
         <v>30</v>
       </c>
+      <c r="C21" s="12">
+        <f>IF($B$16="LEASEHOLD",IF($B$21&gt;0,"","A RENSEIGNER"),"sans objet en FREEHOLD")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -830,22 +867,22 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Taux</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
@@ -857,12 +894,12 @@
           <t>Prix du terrain</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="15">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="16">
         <f>IF($B$16="FREEHOLD",$B$17*$B$19,$B$17*$B$20*$B$21)</f>
         <v/>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="17">
         <f>C26/$B$7</f>
         <v/>
       </c>
@@ -873,15 +910,15 @@
           <t>Taxes gouvernementales</t>
         </is>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="15">
         <f>$B$8</f>
         <v/>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="16">
         <f>C26*$B$8</f>
         <v/>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="17">
         <f>C27/$B$7</f>
         <v/>
       </c>
@@ -892,15 +929,15 @@
           <t>Honoraires du notaire (forfait plancher en B10)</t>
         </is>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="15">
         <f>IF(C26=0,0,C28/C26)</f>
         <v/>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="16">
         <f>MAX(C26*$B$9,$B$10)</f>
         <v/>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="17">
         <f>C28/$B$7</f>
         <v/>
       </c>
@@ -911,15 +948,15 @@
           <t>Sous-total frais de notaire (taxes + honoraires)</t>
         </is>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="15">
         <f>IF(C26=0,0,C29/C26)</f>
         <v/>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="16">
         <f>C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="17">
         <f>C29/$B$7</f>
         <v/>
       </c>
@@ -931,11 +968,11 @@
         </is>
       </c>
       <c r="B30" s="3" t="n"/>
-      <c r="C30" s="15">
+      <c r="C30" s="16">
         <f>$B$11*$B$7</f>
         <v/>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="17">
         <f>$B$11</f>
         <v/>
       </c>
@@ -946,12 +983,12 @@
           <t>Frais d'emménagement</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n"/>
-      <c r="C31" s="15">
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="16">
         <f>$B$22</f>
         <v/>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <f>C31/$B$7</f>
         <v/>
       </c>
@@ -962,28 +999,28 @@
           <t>Cérémonie traditionnelle</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="15">
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="16">
         <f>$B$23</f>
         <v/>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <f>C32/$B$7</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>COÛT FONCIER TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="19">
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="20">
         <f>C26+C29+C30+C31+C32</f>
         <v/>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="21">
         <f>C33/$B$7</f>
         <v/>
       </c>
@@ -1014,35 +1051,35 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr"/>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr"/>
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Désignation de la villa</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>Construction (EUR)</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>Ameublement (EUR)</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Total villa (EUR)</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>Total villa (IDR)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>Villa 1</t>
         </is>
@@ -1054,17 +1091,17 @@
       </c>
       <c r="C39" s="9" t="n"/>
       <c r="D39" s="9" t="n"/>
-      <c r="E39" s="16">
+      <c r="E39" s="17">
         <f>C39+D39</f>
         <v/>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="16">
         <f>E39*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>Villa 2</t>
         </is>
@@ -1072,17 +1109,17 @@
       <c r="B40" s="11" t="n"/>
       <c r="C40" s="9" t="n"/>
       <c r="D40" s="9" t="n"/>
-      <c r="E40" s="16">
+      <c r="E40" s="17">
         <f>C40+D40</f>
         <v/>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="16">
         <f>E40*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>Villa 3</t>
         </is>
@@ -1090,17 +1127,17 @@
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="9" t="n"/>
       <c r="D41" s="9" t="n"/>
-      <c r="E41" s="16">
+      <c r="E41" s="17">
         <f>C41+D41</f>
         <v/>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="16">
         <f>E41*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>Villa 4</t>
         </is>
@@ -1108,17 +1145,17 @@
       <c r="B42" s="11" t="n"/>
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
-      <c r="E42" s="16">
+      <c r="E42" s="17">
         <f>C42+D42</f>
         <v/>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="16">
         <f>E42*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>Villa 5</t>
         </is>
@@ -1126,56 +1163,56 @@
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="9" t="n"/>
-      <c r="E43" s="16">
+      <c r="E43" s="17">
         <f>C43+D43</f>
         <v/>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="16">
         <f>E43*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>TOTAL VILLAS</t>
         </is>
       </c>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="20">
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="21">
         <f>SUM(C39:C43)</f>
         <v/>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="21">
         <f>SUM(D39:D43)</f>
         <v/>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="21">
         <f>SUM(E39:E43)</f>
         <v/>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="20">
         <f>E44*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>Taux</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
@@ -1187,12 +1224,12 @@
           <t>Coût foncier (report du tableau 1)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="n"/>
-      <c r="C47" s="15">
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="16">
         <f>C33</f>
         <v/>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="17">
         <f>C47/$B$7</f>
         <v/>
       </c>
@@ -1203,12 +1240,12 @@
           <t>Constructions et ameublements (total villas)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="n"/>
-      <c r="C48" s="15">
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="16">
         <f>F44</f>
         <v/>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="17">
         <f>C48/$B$7</f>
         <v/>
       </c>
@@ -1219,28 +1256,28 @@
           <t>Création de la PT PMA (si OUI en B36)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="n"/>
-      <c r="C49" s="15">
+      <c r="B49" s="15" t="n"/>
+      <c r="C49" s="16">
         <f>IF($B$36="OUI",$B$12*$B$7,0)</f>
         <v/>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="17">
         <f>C49/$B$7</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>INVESTISSEMENT TOTAL</t>
         </is>
       </c>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="19">
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="20">
         <f>C47+C48+C49</f>
         <v/>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="21">
         <f>C50/$B$7</f>
         <v/>
       </c>
@@ -1269,40 +1306,40 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr"/>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="A55" s="13" t="inlineStr"/>
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>Désignation de la villa</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>Taux d'occupation</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>Prix nuitée (EUR)</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>Nuits occupées / an</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>Revenus bruts (EUR)</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
         <is>
           <t>Revenus bruts (IDR)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>Villa 1</t>
         </is>
@@ -1311,27 +1348,27 @@
         <f>IF($B$39="","",$B$39)</f>
         <v/>
       </c>
-      <c r="C56" s="23" t="n">
+      <c r="C56" s="24" t="n">
         <v>0.65</v>
       </c>
       <c r="D56" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="E56" s="24">
+      <c r="E56" s="25">
         <f>$B$13*C56</f>
         <v/>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="17">
         <f>E56*D56</f>
         <v/>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="16">
         <f>F56*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="inlineStr">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>Villa 2</t>
         </is>
@@ -1340,23 +1377,23 @@
         <f>IF($B$40="","",$B$40)</f>
         <v/>
       </c>
-      <c r="C57" s="23" t="n"/>
+      <c r="C57" s="24" t="n"/>
       <c r="D57" s="9" t="n"/>
-      <c r="E57" s="24">
+      <c r="E57" s="25">
         <f>$B$13*C57</f>
         <v/>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="17">
         <f>E57*D57</f>
         <v/>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="16">
         <f>F57*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="inlineStr">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>Villa 3</t>
         </is>
@@ -1365,23 +1402,23 @@
         <f>IF($B$41="","",$B$41)</f>
         <v/>
       </c>
-      <c r="C58" s="23" t="n"/>
+      <c r="C58" s="24" t="n"/>
       <c r="D58" s="9" t="n"/>
-      <c r="E58" s="24">
+      <c r="E58" s="25">
         <f>$B$13*C58</f>
         <v/>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="17">
         <f>E58*D58</f>
         <v/>
       </c>
-      <c r="G58" s="15">
+      <c r="G58" s="16">
         <f>F58*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="21" t="inlineStr">
+      <c r="A59" s="22" t="inlineStr">
         <is>
           <t>Villa 4</t>
         </is>
@@ -1390,23 +1427,23 @@
         <f>IF($B$42="","",$B$42)</f>
         <v/>
       </c>
-      <c r="C59" s="23" t="n"/>
+      <c r="C59" s="24" t="n"/>
       <c r="D59" s="9" t="n"/>
-      <c r="E59" s="24">
+      <c r="E59" s="25">
         <f>$B$13*C59</f>
         <v/>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="17">
         <f>E59*D59</f>
         <v/>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="16">
         <f>F59*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="21" t="inlineStr">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>Villa 5</t>
         </is>
@@ -1415,77 +1452,77 @@
         <f>IF($B$43="","",$B$43)</f>
         <v/>
       </c>
-      <c r="C60" s="23" t="n"/>
+      <c r="C60" s="24" t="n"/>
       <c r="D60" s="9" t="n"/>
-      <c r="E60" s="24">
+      <c r="E60" s="25">
         <f>$B$13*C60</f>
         <v/>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="17">
         <f>E60*D60</f>
         <v/>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="16">
         <f>F60*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="A61" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B61" s="22" t="n"/>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="22" t="n"/>
-      <c r="E61" s="25">
+      <c r="B61" s="23" t="n"/>
+      <c r="C61" s="23" t="n"/>
+      <c r="D61" s="23" t="n"/>
+      <c r="E61" s="26">
         <f>SUM(E56:E60)</f>
         <v/>
       </c>
-      <c r="F61" s="20">
+      <c r="F61" s="21">
         <f>SUM(F56:F60)</f>
         <v/>
       </c>
-      <c r="G61" s="19">
+      <c r="G61" s="20">
         <f>SUM(G56:G60)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>Taux</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="A64" s="18" t="inlineStr">
         <is>
           <t>REVENUS BRUTS ANNUELS</t>
         </is>
       </c>
-      <c r="B64" s="22" t="n"/>
-      <c r="C64" s="19">
+      <c r="B64" s="23" t="n"/>
+      <c r="C64" s="20">
         <f>G61</f>
         <v/>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="21">
         <f>F61</f>
         <v/>
       </c>
@@ -1496,31 +1533,31 @@
           <t>Charges d'exploitation</t>
         </is>
       </c>
-      <c r="B65" s="14">
+      <c r="B65" s="15">
         <f>$B$53</f>
         <v/>
       </c>
-      <c r="C65" s="15">
+      <c r="C65" s="16">
         <f>C64*$B$53</f>
         <v/>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="17">
         <f>C65/$B$7</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>REVENUS NETS ANNUELS</t>
         </is>
       </c>
-      <c r="B66" s="18" t="n"/>
-      <c r="C66" s="19">
+      <c r="B66" s="19" t="n"/>
+      <c r="C66" s="20">
         <f>C64-C65</f>
         <v/>
       </c>
-      <c r="D66" s="20">
+      <c r="D66" s="21">
         <f>C66/$B$7</f>
         <v/>
       </c>
@@ -1544,7 +1581,7 @@
           <t>Nombre de villas retenues dans le scénario</t>
         </is>
       </c>
-      <c r="B69" s="26">
+      <c r="B69" s="27">
         <f>COUNTIF(D56:D60,"&gt;0")</f>
         <v/>
       </c>
@@ -1555,7 +1592,7 @@
           <t>Rendement brut (revenus bruts / investissement total)</t>
         </is>
       </c>
-      <c r="B70" s="18">
+      <c r="B70" s="19">
         <f>IF(C50=0,0,C64/C50)</f>
         <v/>
       </c>
@@ -1566,7 +1603,7 @@
           <t>Rendement net (revenus nets / investissement total)</t>
         </is>
       </c>
-      <c r="B71" s="18">
+      <c r="B71" s="19">
         <f>IF(C50=0,0,C66/C50)</f>
         <v/>
       </c>
@@ -1577,19 +1614,34 @@
           <t>Retour sur investissement (années)</t>
         </is>
       </c>
-      <c r="B72" s="27">
+      <c r="B72" s="28">
         <f>IF(C66=0,0,C50/C66)</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="28" t="inlineStr">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Document établi à titre indicatif, sans valeur contractuelle.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A19:C19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$B$16&lt;&gt;"FREEHOLD"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:C20">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$B$16&lt;&gt;"LEASEHOLD"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:C21">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>$B$16&lt;&gt;"LEASEHOLD"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"FREEHOLD,LEASEHOLD"</formula1>

--- a/transactions/Projection_de_projet_CLIENT.xlsx
+++ b/transactions/Projection_de_projet_CLIENT.xlsx
@@ -331,12 +331,17 @@
         <t>Pourcentage appliqué au revenu brut cumulé de toutes les villas (gestion, ménage, entretien, énergie...).</t>
       </text>
     </comment>
-    <comment ref="C56" authorId="0" shapeId="0">
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Impôt assis sur le chiffre d'affaires brut, et non sur le résultat : il est dû même si l'exploitation ne dégage pas de bénéfice.</t>
+      </text>
+    </comment>
+    <comment ref="C57" authorId="0" shapeId="0">
       <text>
         <t>Taux d'occupation propre à cette villa (ex. 65% = 237 nuits sur 365).</t>
       </text>
     </comment>
-    <comment ref="D56" authorId="0" shapeId="0">
+    <comment ref="D57" authorId="0" shapeId="0">
       <text>
         <t>Prix moyen de la nuitée de cette villa, en EUR. Laisser vide si la villa n'est pas utilisee dans ce scenario.</t>
       </text>
@@ -634,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1305,80 +1310,65 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr"/>
-      <c r="B55" s="14" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Impôt sur les sociétés (% du chiffre d'affaires)</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr"/>
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>Désignation de la villa</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>Taux d'occupation</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>Prix nuitée (EUR)</t>
         </is>
       </c>
-      <c r="E55" s="14" t="inlineStr">
+      <c r="E56" s="14" t="inlineStr">
         <is>
           <t>Nuits occupées / an</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F56" s="14" t="inlineStr">
         <is>
           <t>Revenus bruts (EUR)</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>Revenus bruts (IDR)</t>
         </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="22" t="inlineStr">
-        <is>
-          <t>Villa 1</t>
-        </is>
-      </c>
-      <c r="B56" s="3">
-        <f>IF($B$39="","",$B$39)</f>
-        <v/>
-      </c>
-      <c r="C56" s="24" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D56" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="E56" s="25">
-        <f>$B$13*C56</f>
-        <v/>
-      </c>
-      <c r="F56" s="17">
-        <f>E56*D56</f>
-        <v/>
-      </c>
-      <c r="G56" s="16">
-        <f>F56*$B$7</f>
-        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>Villa 2</t>
+          <t>Villa 1</t>
         </is>
       </c>
       <c r="B57" s="3">
-        <f>IF($B$40="","",$B$40)</f>
-        <v/>
-      </c>
-      <c r="C57" s="24" t="n"/>
-      <c r="D57" s="9" t="n"/>
+        <f>IF($B$39="","",$B$39)</f>
+        <v/>
+      </c>
+      <c r="C57" s="24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>250</v>
+      </c>
       <c r="E57" s="25">
         <f>$B$13*C57</f>
         <v/>
@@ -1395,11 +1385,11 @@
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>Villa 3</t>
+          <t>Villa 2</t>
         </is>
       </c>
       <c r="B58" s="3">
-        <f>IF($B$41="","",$B$41)</f>
+        <f>IF($B$40="","",$B$40)</f>
         <v/>
       </c>
       <c r="C58" s="24" t="n"/>
@@ -1420,11 +1410,11 @@
     <row r="59">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>Villa 4</t>
+          <t>Villa 3</t>
         </is>
       </c>
       <c r="B59" s="3">
-        <f>IF($B$42="","",$B$42)</f>
+        <f>IF($B$41="","",$B$41)</f>
         <v/>
       </c>
       <c r="C59" s="24" t="n"/>
@@ -1445,11 +1435,11 @@
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>Villa 5</t>
+          <t>Villa 4</t>
         </is>
       </c>
       <c r="B60" s="3">
-        <f>IF($B$43="","",$B$43)</f>
+        <f>IF($B$42="","",$B$42)</f>
         <v/>
       </c>
       <c r="C60" s="24" t="n"/>
@@ -1468,159 +1458,222 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Villa 5</t>
+        </is>
+      </c>
+      <c r="B61" s="3">
+        <f>IF($B$43="","",$B$43)</f>
+        <v/>
+      </c>
+      <c r="C61" s="24" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="25">
+        <f>$B$13*C61</f>
+        <v/>
+      </c>
+      <c r="F61" s="17">
+        <f>E61*D61</f>
+        <v/>
+      </c>
+      <c r="G61" s="16">
+        <f>F61*$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B61" s="23" t="n"/>
-      <c r="C61" s="23" t="n"/>
-      <c r="D61" s="23" t="n"/>
-      <c r="E61" s="26">
-        <f>SUM(E56:E60)</f>
-        <v/>
-      </c>
-      <c r="F61" s="21">
-        <f>SUM(F56:F60)</f>
-        <v/>
-      </c>
-      <c r="G61" s="20">
-        <f>SUM(G56:G60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="B62" s="23" t="n"/>
+      <c r="C62" s="23" t="n"/>
+      <c r="D62" s="23" t="n"/>
+      <c r="E62" s="26">
+        <f>SUM(E57:E61)</f>
+        <v/>
+      </c>
+      <c r="F62" s="21">
+        <f>SUM(F57:F61)</f>
+        <v/>
+      </c>
+      <c r="G62" s="20">
+        <f>SUM(G57:G61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>Taux</t>
         </is>
       </c>
-      <c r="C63" s="14" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t>REVENUS BRUTS ANNUELS</t>
         </is>
       </c>
-      <c r="B64" s="23" t="n"/>
-      <c r="C64" s="20">
-        <f>G61</f>
-        <v/>
-      </c>
-      <c r="D64" s="21">
-        <f>F61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="B65" s="23" t="n"/>
+      <c r="C65" s="20">
+        <f>G62</f>
+        <v/>
+      </c>
+      <c r="D65" s="21">
+        <f>F62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Charges d'exploitation</t>
         </is>
       </c>
-      <c r="B65" s="15">
+      <c r="B66" s="15">
         <f>$B$53</f>
         <v/>
       </c>
-      <c r="C65" s="16">
-        <f>C64*$B$53</f>
-        <v/>
-      </c>
-      <c r="D65" s="17">
-        <f>C65/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="C66" s="16">
+        <f>C65*$B$53</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>C66/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Impôt sur les sociétés (sur le chiffre d'affaires)</t>
+        </is>
+      </c>
+      <c r="B67" s="15">
+        <f>$B$54</f>
+        <v/>
+      </c>
+      <c r="C67" s="16">
+        <f>C65*$B$54</f>
+        <v/>
+      </c>
+      <c r="D67" s="17">
+        <f>C67/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL DES CHARGES</t>
+        </is>
+      </c>
+      <c r="B68" s="15">
+        <f>IF(C65=0,0,C68/C65)</f>
+        <v/>
+      </c>
+      <c r="C68" s="16">
+        <f>C66+C67</f>
+        <v/>
+      </c>
+      <c r="D68" s="17">
+        <f>C68/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>REVENUS NETS ANNUELS</t>
         </is>
       </c>
-      <c r="B66" s="19" t="n"/>
-      <c r="C66" s="20">
-        <f>C64-C65</f>
-        <v/>
-      </c>
-      <c r="D66" s="21">
-        <f>C66/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="B69" s="19" t="n"/>
+      <c r="C69" s="20">
+        <f>C65-C68</f>
+        <v/>
+      </c>
+      <c r="D69" s="21">
+        <f>C69/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>INDICATEURS</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Nombre de villas retenues dans le scénario</t>
-        </is>
-      </c>
-      <c r="B69" s="27">
-        <f>COUNTIF(D56:D60,"&gt;0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Rendement brut (revenus bruts / investissement total)</t>
-        </is>
-      </c>
-      <c r="B70" s="19">
-        <f>IF(C50=0,0,C64/C50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Rendement net (revenus nets / investissement total)</t>
-        </is>
-      </c>
-      <c r="B71" s="19">
-        <f>IF(C50=0,0,C66/C50)</f>
-        <v/>
-      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
+          <t>Nombre de villas retenues dans le scénario</t>
+        </is>
+      </c>
+      <c r="B72" s="27">
+        <f>COUNTIF(D57:D61,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Rendement brut (revenus bruts / investissement total)</t>
+        </is>
+      </c>
+      <c r="B73" s="19">
+        <f>IF(C50=0,0,C65/C50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Rendement net (revenus nets / investissement total)</t>
+        </is>
+      </c>
+      <c r="B74" s="19">
+        <f>IF(C50=0,0,C69/C50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
           <t>Retour sur investissement (années)</t>
         </is>
       </c>
-      <c r="B72" s="28">
-        <f>IF(C66=0,0,C50/C66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+      <c r="B75" s="28">
+        <f>IF(C69=0,0,C50/C69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Document établi à titre indicatif, sans valeur contractuelle.</t>
         </is>

--- a/transactions/Projection_de_projet_CLIENT.xlsx
+++ b/transactions/Projection_de_projet_CLIENT.xlsx
@@ -294,54 +294,59 @@
         <t>Cérémonie traditionnelle balinaise. Montant forfaitaire a renseigner selon le dossier.</t>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Montant à renseigner manuellement selon le dossier.</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0" shapeId="0">
       <text>
         <t>FREEHOLD : surface x prix à l'are.
 LEASEHOLD : surface x prix à l'are et par an x durée.</t>
       </text>
     </comment>
-    <comment ref="C28" authorId="0" shapeId="0">
+    <comment ref="C31" authorId="0" shapeId="0">
       <text>
         <t>MAX entre le pourcentage d'honoraires (B9) et le forfait minimum (B10) : si le pourcentage donne moins que le forfait, c'est le forfait qui s'applique.</t>
       </text>
     </comment>
-    <comment ref="B36" authorId="0" shapeId="0">
+    <comment ref="B39" authorId="0" shapeId="0">
       <text>
         <t>Case à cocher : OUI ajoute les 2 000 EUR de creation de la PT PMA (cellule B12) a l'investissement, NON les retire.</t>
       </text>
     </comment>
-    <comment ref="B39" authorId="0" shapeId="0">
+    <comment ref="B42" authorId="0" shapeId="0">
       <text>
         <t>Nommer chaque villa ici (villa principale, villa 2 chambres, pool house...). La désignation est reprise automatiquement dans le tableau des revenus.
 Laisser vide les villas non utilisées : elles comptent pour zéro.</t>
       </text>
     </comment>
-    <comment ref="C39" authorId="0" shapeId="0">
+    <comment ref="C42" authorId="0" shapeId="0">
       <text>
         <t>Budget de construction en EUR. Pour un devis exprimé en IDR, saisir la formule =montant_IDR/$B$7.</t>
       </text>
     </comment>
-    <comment ref="D39" authorId="0" shapeId="0">
+    <comment ref="D42" authorId="0" shapeId="0">
       <text>
         <t>Budget d'ameublement en EUR. Pour un devis exprimé en IDR, saisir la formule =montant_IDR/$B$7.</t>
       </text>
     </comment>
-    <comment ref="B53" authorId="0" shapeId="0">
+    <comment ref="B56" authorId="0" shapeId="0">
       <text>
         <t>Pourcentage appliqué au revenu brut cumulé de toutes les villas (gestion, ménage, entretien, énergie...).</t>
       </text>
     </comment>
-    <comment ref="B54" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <t>Impôt assis sur le chiffre d'affaires brut, et non sur le résultat : il est dû même si l'exploitation ne dégage pas de bénéfice.</t>
       </text>
     </comment>
-    <comment ref="C57" authorId="0" shapeId="0">
+    <comment ref="C60" authorId="0" shapeId="0">
       <text>
         <t>Taux d'occupation propre à cette villa (ex. 65% = 237 nuits sur 365).</t>
       </text>
     </comment>
-    <comment ref="D57" authorId="0" shapeId="0">
+    <comment ref="D60" authorId="0" shapeId="0">
       <text>
         <t>Prix moyen de la nuitée de cette villa, en EUR. Laisser vide si la villa n'est pas utilisee dans ce scenario.</t>
       </text>
@@ -639,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -830,7 +835,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="C20" s="12">
         <f>IF($B$16="LEASEHOLD",IF($B$20&gt;0,"","A RENSEIGNER"),"sans objet en FREEHOLD")</f>
@@ -871,56 +876,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Frais d'agence (IDR)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Taux</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Prix du terrain</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="16">
-        <f>IF($B$16="FREEHOLD",$B$17*$B$19,$B$17*$B$20*$B$21)</f>
-        <v/>
-      </c>
-      <c r="D26" s="17">
-        <f>C26/$B$7</f>
-        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Taxes gouvernementales</t>
-        </is>
-      </c>
-      <c r="B27" s="15">
-        <f>$B$8</f>
-        <v/>
-      </c>
+          <t>Prix du terrain</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="16">
-        <f>C26*$B$8</f>
+        <f>IF($B$16="FREEHOLD",$B$17*$B$19,$B$17*$B$20*$B$21)</f>
         <v/>
       </c>
       <c r="D27" s="17">
@@ -931,15 +927,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (forfait plancher en B10)</t>
-        </is>
-      </c>
-      <c r="B28" s="15">
-        <f>IF(C26=0,0,C28/C26)</f>
-        <v/>
-      </c>
+          <t>Frais d'agence</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n"/>
       <c r="C28" s="16">
-        <f>MAX(C26*$B$9,$B$10)</f>
+        <f>$B$24</f>
         <v/>
       </c>
       <c r="D28" s="17">
@@ -948,20 +941,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Sous-total frais de notaire (taxes + honoraires)</t>
-        </is>
-      </c>
-      <c r="B29" s="15">
-        <f>IF(C26=0,0,C29/C26)</f>
-        <v/>
-      </c>
-      <c r="C29" s="16">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL TERRAIN ET FRAIS D'AGENCE</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="20">
         <f>C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="21">
         <f>C29/$B$7</f>
         <v/>
       </c>
@@ -969,28 +959,34 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Frais de géomètre (forfait)</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n"/>
+          <t>Taxes gouvernementales</t>
+        </is>
+      </c>
+      <c r="B30" s="15">
+        <f>$B$8</f>
+        <v/>
+      </c>
       <c r="C30" s="16">
-        <f>$B$11*$B$7</f>
+        <f>C29*$B$8</f>
         <v/>
       </c>
       <c r="D30" s="17">
-        <f>$B$11</f>
+        <f>C30/$B$7</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Frais d'emménagement</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n"/>
+          <t>Honoraires du notaire (forfait plancher en B10)</t>
+        </is>
+      </c>
+      <c r="B31" s="15">
+        <f>IF(C29=0,0,C31/C29)</f>
+        <v/>
+      </c>
       <c r="C31" s="16">
-        <f>$B$22</f>
+        <f>MAX(C29*$B$9,$B$10)</f>
         <v/>
       </c>
       <c r="D31" s="17">
@@ -1001,12 +997,15 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Cérémonie traditionnelle</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n"/>
+          <t>Sous-total frais de notaire (taxes + honoraires)</t>
+        </is>
+      </c>
+      <c r="B32" s="15">
+        <f>IF(C29=0,0,C32/C29)</f>
+        <v/>
+      </c>
       <c r="C32" s="16">
-        <f>$B$23</f>
+        <f>C30+C31</f>
         <v/>
       </c>
       <c r="D32" s="17">
@@ -1015,139 +1014,133 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Frais de géomètre (forfait)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="16">
+        <f>$B$11*$B$7</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Frais d'emménagement</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="16">
+        <f>$B$22</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>C34/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Cérémonie traditionnelle</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="16">
+        <f>$B$23</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>C35/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>COÛT FONCIER TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="20">
-        <f>C26+C29+C30+C31+C32</f>
-        <v/>
-      </c>
-      <c r="D33" s="21">
-        <f>C33/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="20">
+        <f>C29+C32+C33+C34+C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="21">
+        <f>C36/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>2. INVESTISSEMENT À CONSENTIR</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Création de la PT PMA - à inclure ? (OUI / NON)</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr"/>
-      <c r="B38" s="14" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr"/>
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>Désignation de la villa</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>Construction (EUR)</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>Ameublement (EUR)</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>Total villa (EUR)</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Total villa (IDR)</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>Villa 1</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Villa 1</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="17">
-        <f>C39+D39</f>
-        <v/>
-      </c>
-      <c r="F39" s="16">
-        <f>E39*$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>Villa 2</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="17">
-        <f>C40+D40</f>
-        <v/>
-      </c>
-      <c r="F40" s="16">
-        <f>E40*$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>Villa 3</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="17">
-        <f>C41+D41</f>
-        <v/>
-      </c>
-      <c r="F41" s="16">
-        <f>E41*$B$7</f>
-        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>Villa 4</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n"/>
+          <t>Villa 1</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Villa 1</t>
+        </is>
+      </c>
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="17">
@@ -1162,7 +1155,7 @@
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>Villa 5</t>
+          <t>Villa 2</t>
         </is>
       </c>
       <c r="B43" s="11" t="n"/>
@@ -1178,272 +1171,251 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Villa 3</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="17">
+        <f>C44+D44</f>
+        <v/>
+      </c>
+      <c r="F44" s="16">
+        <f>E44*$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>Villa 4</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="17">
+        <f>C45+D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="16">
+        <f>E45*$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Villa 5</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="17">
+        <f>C46+D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="16">
+        <f>E46*$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>TOTAL VILLAS</t>
         </is>
       </c>
-      <c r="B44" s="23" t="n"/>
-      <c r="C44" s="21">
-        <f>SUM(C39:C43)</f>
-        <v/>
-      </c>
-      <c r="D44" s="21">
-        <f>SUM(D39:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="21">
-        <f>SUM(E39:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="20">
-        <f>E44*$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="21">
+        <f>SUM(C42:C46)</f>
+        <v/>
+      </c>
+      <c r="D47" s="21">
+        <f>SUM(D42:D46)</f>
+        <v/>
+      </c>
+      <c r="E47" s="21">
+        <f>SUM(E42:E46)</f>
+        <v/>
+      </c>
+      <c r="F47" s="20">
+        <f>E47*$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>Taux</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>Montant IDR</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>Montant EUR</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Coût foncier (report du tableau 1)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="16">
-        <f>C33</f>
-        <v/>
-      </c>
-      <c r="D47" s="17">
-        <f>C47/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="B50" s="15" t="n"/>
+      <c r="C50" s="16">
+        <f>C36</f>
+        <v/>
+      </c>
+      <c r="D50" s="17">
+        <f>C50/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Constructions et ameublements (total villas)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="n"/>
-      <c r="C48" s="16">
-        <f>F44</f>
-        <v/>
-      </c>
-      <c r="D48" s="17">
-        <f>C48/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Création de la PT PMA (si OUI en B36)</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="16">
-        <f>IF($B$36="OUI",$B$12*$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="D49" s="17">
-        <f>C49/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="16">
+        <f>F47</f>
+        <v/>
+      </c>
+      <c r="D51" s="17">
+        <f>C51/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Création de la PT PMA (si OUI en B39)</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="n"/>
+      <c r="C52" s="16">
+        <f>IF($B$39="OUI",$B$12*$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="D52" s="17">
+        <f>C52/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>INVESTISSEMENT TOTAL</t>
         </is>
       </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="20">
-        <f>C47+C48+C49</f>
-        <v/>
-      </c>
-      <c r="D50" s="21">
-        <f>C50/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="B53" s="19" t="n"/>
+      <c r="C53" s="20">
+        <f>C50+C51+C52</f>
+        <v/>
+      </c>
+      <c r="D53" s="21">
+        <f>C53/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>3. REVENUS PRÉVISIONNELS PAR VILLA</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Charges d'exploitation (% du revenu brut)</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
+      <c r="B56" s="7" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Impôt sur les sociétés (% du chiffre d'affaires)</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B57" s="7" t="n">
         <v>0.005</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr"/>
-      <c r="B56" s="14" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr"/>
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>Désignation de la villa</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>Taux d'occupation</t>
         </is>
       </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>Prix nuitée (EUR)</t>
         </is>
       </c>
-      <c r="E56" s="14" t="inlineStr">
+      <c r="E59" s="14" t="inlineStr">
         <is>
           <t>Nuits occupées / an</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="F59" s="14" t="inlineStr">
         <is>
           <t>Revenus bruts (EUR)</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
+      <c r="G59" s="14" t="inlineStr">
         <is>
           <t>Revenus bruts (IDR)</t>
         </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>Villa 1</t>
-        </is>
-      </c>
-      <c r="B57" s="3">
-        <f>IF($B$39="","",$B$39)</f>
-        <v/>
-      </c>
-      <c r="C57" s="24" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D57" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="E57" s="25">
-        <f>$B$13*C57</f>
-        <v/>
-      </c>
-      <c r="F57" s="17">
-        <f>E57*D57</f>
-        <v/>
-      </c>
-      <c r="G57" s="16">
-        <f>F57*$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="22" t="inlineStr">
-        <is>
-          <t>Villa 2</t>
-        </is>
-      </c>
-      <c r="B58" s="3">
-        <f>IF($B$40="","",$B$40)</f>
-        <v/>
-      </c>
-      <c r="C58" s="24" t="n"/>
-      <c r="D58" s="9" t="n"/>
-      <c r="E58" s="25">
-        <f>$B$13*C58</f>
-        <v/>
-      </c>
-      <c r="F58" s="17">
-        <f>E58*D58</f>
-        <v/>
-      </c>
-      <c r="G58" s="16">
-        <f>F58*$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="22" t="inlineStr">
-        <is>
-          <t>Villa 3</t>
-        </is>
-      </c>
-      <c r="B59" s="3">
-        <f>IF($B$41="","",$B$41)</f>
-        <v/>
-      </c>
-      <c r="C59" s="24" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="25">
-        <f>$B$13*C59</f>
-        <v/>
-      </c>
-      <c r="F59" s="17">
-        <f>E59*D59</f>
-        <v/>
-      </c>
-      <c r="G59" s="16">
-        <f>F59*$B$7</f>
-        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>Villa 4</t>
+          <t>Villa 1</t>
         </is>
       </c>
       <c r="B60" s="3">
         <f>IF($B$42="","",$B$42)</f>
         <v/>
       </c>
-      <c r="C60" s="24" t="n"/>
-      <c r="D60" s="9" t="n"/>
+      <c r="C60" s="24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>250</v>
+      </c>
       <c r="E60" s="25">
         <f>$B$13*C60</f>
         <v/>
@@ -1460,7 +1432,7 @@
     <row r="61">
       <c r="A61" s="22" t="inlineStr">
         <is>
-          <t>Villa 5</t>
+          <t>Villa 2</t>
         </is>
       </c>
       <c r="B61" s="3">
@@ -1483,197 +1455,272 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B62" s="23" t="n"/>
-      <c r="C62" s="23" t="n"/>
-      <c r="D62" s="23" t="n"/>
-      <c r="E62" s="26">
-        <f>SUM(E57:E61)</f>
-        <v/>
-      </c>
-      <c r="F62" s="21">
-        <f>SUM(F57:F61)</f>
-        <v/>
-      </c>
-      <c r="G62" s="20">
-        <f>SUM(G57:G61)</f>
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Villa 3</t>
+        </is>
+      </c>
+      <c r="B62" s="3">
+        <f>IF($B$44="","",$B$44)</f>
+        <v/>
+      </c>
+      <c r="C62" s="24" t="n"/>
+      <c r="D62" s="9" t="n"/>
+      <c r="E62" s="25">
+        <f>$B$13*C62</f>
+        <v/>
+      </c>
+      <c r="F62" s="17">
+        <f>E62*D62</f>
+        <v/>
+      </c>
+      <c r="G62" s="16">
+        <f>F62*$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Villa 4</t>
+        </is>
+      </c>
+      <c r="B63" s="3">
+        <f>IF($B$45="","",$B$45)</f>
+        <v/>
+      </c>
+      <c r="C63" s="24" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="25">
+        <f>$B$13*C63</f>
+        <v/>
+      </c>
+      <c r="F63" s="17">
+        <f>E63*D63</f>
+        <v/>
+      </c>
+      <c r="G63" s="16">
+        <f>F63*$B$7</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>Poste</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>Taux</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>Montant IDR</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Montant EUR</t>
-        </is>
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Villa 5</t>
+        </is>
+      </c>
+      <c r="B64" s="3">
+        <f>IF($B$46="","",$B$46)</f>
+        <v/>
+      </c>
+      <c r="C64" s="24" t="n"/>
+      <c r="D64" s="9" t="n"/>
+      <c r="E64" s="25">
+        <f>$B$13*C64</f>
+        <v/>
+      </c>
+      <c r="F64" s="17">
+        <f>E64*D64</f>
+        <v/>
+      </c>
+      <c r="G64" s="16">
+        <f>F64*$B$7</f>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="18" t="inlineStr">
         <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="n"/>
+      <c r="C65" s="23" t="n"/>
+      <c r="D65" s="23" t="n"/>
+      <c r="E65" s="26">
+        <f>SUM(E60:E64)</f>
+        <v/>
+      </c>
+      <c r="F65" s="21">
+        <f>SUM(F60:F64)</f>
+        <v/>
+      </c>
+      <c r="G65" s="20">
+        <f>SUM(G60:G64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Taux</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Montant IDR</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>Montant EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
           <t>REVENUS BRUTS ANNUELS</t>
         </is>
       </c>
-      <c r="B65" s="23" t="n"/>
-      <c r="C65" s="20">
-        <f>G62</f>
-        <v/>
-      </c>
-      <c r="D65" s="21">
-        <f>F62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="B68" s="23" t="n"/>
+      <c r="C68" s="20">
+        <f>G65</f>
+        <v/>
+      </c>
+      <c r="D68" s="21">
+        <f>F65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Charges d'exploitation</t>
         </is>
       </c>
-      <c r="B66" s="15">
-        <f>$B$53</f>
-        <v/>
-      </c>
-      <c r="C66" s="16">
-        <f>C65*$B$53</f>
-        <v/>
-      </c>
-      <c r="D66" s="17">
-        <f>C66/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="B69" s="15">
+        <f>$B$56</f>
+        <v/>
+      </c>
+      <c r="C69" s="16">
+        <f>C68*$B$56</f>
+        <v/>
+      </c>
+      <c r="D69" s="17">
+        <f>C69/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Impôt sur les sociétés (sur le chiffre d'affaires)</t>
         </is>
       </c>
-      <c r="B67" s="15">
-        <f>$B$54</f>
-        <v/>
-      </c>
-      <c r="C67" s="16">
-        <f>C65*$B$54</f>
-        <v/>
-      </c>
-      <c r="D67" s="17">
-        <f>C67/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="B70" s="15">
+        <f>$B$57</f>
+        <v/>
+      </c>
+      <c r="C70" s="16">
+        <f>C68*$B$57</f>
+        <v/>
+      </c>
+      <c r="D70" s="17">
+        <f>C70/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>TOTAL DES CHARGES</t>
         </is>
       </c>
-      <c r="B68" s="15">
-        <f>IF(C65=0,0,C68/C65)</f>
-        <v/>
-      </c>
-      <c r="C68" s="16">
-        <f>C66+C67</f>
-        <v/>
-      </c>
-      <c r="D68" s="17">
-        <f>C68/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="B71" s="15">
+        <f>IF(C68=0,0,C71/C68)</f>
+        <v/>
+      </c>
+      <c r="C71" s="16">
+        <f>C69+C70</f>
+        <v/>
+      </c>
+      <c r="D71" s="17">
+        <f>C71/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
         <is>
           <t>REVENUS NETS ANNUELS</t>
         </is>
       </c>
-      <c r="B69" s="19" t="n"/>
-      <c r="C69" s="20">
-        <f>C65-C68</f>
-        <v/>
-      </c>
-      <c r="D69" s="21">
-        <f>C69/$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="B72" s="19" t="n"/>
+      <c r="C72" s="20">
+        <f>C68-C71</f>
+        <v/>
+      </c>
+      <c r="D72" s="21">
+        <f>C72/$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>INDICATEURS</t>
         </is>
       </c>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Nombre de villas retenues dans le scénario</t>
-        </is>
-      </c>
-      <c r="B72" s="27">
-        <f>COUNTIF(D57:D61,"&gt;0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Rendement brut (revenus bruts / investissement total)</t>
-        </is>
-      </c>
-      <c r="B73" s="19">
-        <f>IF(C50=0,0,C65/C50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Rendement net (revenus nets / investissement total)</t>
-        </is>
-      </c>
-      <c r="B74" s="19">
-        <f>IF(C50=0,0,C69/C50)</f>
-        <v/>
-      </c>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>Nombre de villas retenues dans le scénario</t>
+        </is>
+      </c>
+      <c r="B75" s="27">
+        <f>COUNTIF(D60:D64,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Rendement brut (revenus bruts / investissement total)</t>
+        </is>
+      </c>
+      <c r="B76" s="19">
+        <f>IF(C53=0,0,C68/C53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Rendement net (revenus nets / investissement total)</t>
+        </is>
+      </c>
+      <c r="B77" s="19">
+        <f>IF(C53=0,0,C72/C53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
           <t>Retour sur investissement (années)</t>
         </is>
       </c>
-      <c r="B75" s="28">
-        <f>IF(C69=0,0,C50/C69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+      <c r="B78" s="28">
+        <f>IF(C72=0,0,C53/C72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>Document établi à titre indicatif, sans valeur contractuelle.</t>
         </is>
@@ -1699,7 +1746,7 @@
     <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"FREEHOLD,LEASEHOLD"</formula1>
     </dataValidation>
-    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OUI,NON"</formula1>
     </dataValidation>
   </dataValidations>

--- a/transactions/Projection_de_projet_CLIENT.xlsx
+++ b/transactions/Projection_de_projet_CLIENT.xlsx
@@ -959,7 +959,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Taxes gouvernementales</t>
+          <t>Taxes gouvernementales (sur le prix officiel du terrain)</t>
         </is>
       </c>
       <c r="B30" s="15">
@@ -967,7 +967,7 @@
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>C29*$B$8</f>
+        <f>C27*$B$8</f>
         <v/>
       </c>
       <c r="D30" s="17">
@@ -978,15 +978,15 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Honoraires du notaire (forfait plancher en B10)</t>
+          <t>Honoraires du notaire (sur le prix officiel, forfait plancher en B10)</t>
         </is>
       </c>
       <c r="B31" s="15">
-        <f>IF(C29=0,0,C31/C29)</f>
+        <f>IF(C27=0,0,C31/C27)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>MAX(C29*$B$9,$B$10)</f>
+        <f>MAX(C27*$B$9,$B$10)</f>
         <v/>
       </c>
       <c r="D31" s="17">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="B32" s="15">
-        <f>IF(C29=0,0,C32/C29)</f>
+        <f>IF(C27=0,0,C32/C27)</f>
         <v/>
       </c>
       <c r="C32" s="16">
